--- a/KatalonData/ABPTestDataDemo/PaymentsCC_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/PaymentsCC_Demo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F12B75-AFD9-42A7-ADBF-3850D6DA534B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36AD63D-BE5F-405C-B2D3-1C32BE940C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VerifySuccessfulPaymentCCNoCF" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="69">
   <si>
     <t>Result</t>
   </si>
@@ -241,56 +241,49 @@
 Country:,	UNITED STATES,</t>
   </si>
   <si>
-    <t>Tue Dec 16 19:24:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:21:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 06 23:56:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 06 23:57:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 06 23:58:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 06 23:58:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jul 07 00:57:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 15:05:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 15:09:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 15:10:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 15:15:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 15:15:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 15:16:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 15:47:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 24 18:03:01 IST 2026</t>
+    <t>Wed Oct 07 22:54:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:00:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:00:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:01:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:02:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:04:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:00:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:11:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:12:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:24:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:35:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:36:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 22:03:09 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -684,8 +677,8 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="3" max="3" customWidth="true" width="22.08984375"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -721,11 +714,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>63</v>
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -749,11 +742,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>64</v>
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -775,11 +768,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>65</v>
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -813,11 +806,11 @@
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" customWidth="true" width="11.36328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" width="17.1796875" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" width="13.0" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" width="12.90625" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" width="12.36328125" collapsed="true"/>
+    <col min="7" max="7" width="11.36328125" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="17.1796875" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="13" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="12.90625" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="12.36328125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="29" x14ac:dyDescent="0.35">
@@ -868,11 +861,11 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>57</v>
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -914,9 +907,9 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" customWidth="true" width="15.453125" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="16.7265625" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="20.453125" collapsed="true"/>
+    <col min="7" max="7" width="15.453125" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.7265625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="20.453125" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -941,19 +934,19 @@
       <c r="G1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>59</v>
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -965,22 +958,22 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str" s="0">
+      <c r="G2" t="str">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s" s="0">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>37</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -992,22 +985,22 @@
       <c r="F3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="str" s="0">
+      <c r="G3" t="str">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H3" t="s" s="0">
+      <c r="H3" t="s">
         <v>33</v>
       </c>
-      <c r="I3" t="s" s="0">
+      <c r="I3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="7" t="s">
@@ -1019,11 +1012,11 @@
       <c r="F4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G4" t="str" s="0">
+      <c r="G4" t="str">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H4" t="s" s="0">
+      <c r="H4" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1048,10 +1041,10 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.90625" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.7265625" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="20.453125" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="20.90625" collapsed="true"/>
+    <col min="7" max="7" width="14.90625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="15.7265625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="20.453125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="20.90625" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1076,22 +1069,22 @@
       <c r="G1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>30</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>58</v>
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1103,25 +1096,25 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str" s="0">
+      <c r="G2" t="str">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>40</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -1133,14 +1126,14 @@
       <c r="F3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="str" s="0">
+      <c r="G3" t="str">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H3" t="s" s="0">
+      <c r="H3" t="s">
         <v>35</v>
       </c>
-      <c r="I3" t="s" s="0">
+      <c r="I3" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1154,8 +1147,8 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="20.453125" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="20.90625" collapsed="true"/>
+    <col min="9" max="9" width="20.453125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="20.90625" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1180,21 +1173,21 @@
       <c r="G1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>30</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s" s="0">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>49</v>
       </c>
       <c r="C2" s="9"/>
@@ -1207,17 +1200,17 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str" s="0">
+      <c r="G2" t="str">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1253,22 +1246,22 @@
       <c r="G1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>30</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>60</v>
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1280,17 +1273,17 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str" s="0">
+      <c r="G2" t="str">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>33</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1326,22 +1319,22 @@
       <c r="G1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>30</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>61</v>
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1353,17 +1346,17 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str" s="0">
+      <c r="G2" t="str">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>33</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>36</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1399,18 +1392,18 @@
       <c r="G1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>38</v>
       </c>
       <c r="D2" s="7" t="s">
@@ -1422,14 +1415,14 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str" s="0">
+      <c r="G2" t="str">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>34</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1443,7 +1436,7 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="12" max="12" customWidth="true" width="9.81640625" collapsed="true"/>
+    <col min="12" max="12" width="9.81640625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
@@ -1485,11 +1478,11 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>70</v>
+      <c r="B2" t="s">
+        <v>61</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1519,10 +1512,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s" s="0">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="3"/>
@@ -1545,10 +1538,10 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s" s="0">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="3"/>
@@ -1580,7 +1573,7 @@
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="31.0" collapsed="true"/>
+    <col min="11" max="11" width="31" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
@@ -1620,10 +1613,10 @@
       <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" ht="145" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s" s="0">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>44</v>
       </c>
       <c r="C2" s="3"/>
@@ -1661,7 +1654,7 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="19.81640625"/>
+    <col min="2" max="2" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -1697,11 +1690,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>66</v>
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1725,16 +1718,14 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>67</v>
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="D3" s="1"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3">
         <v>1</v>
@@ -1751,16 +1742,14 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>68</v>
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>67</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="D4" s="1"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3">
         <v>1</v>
@@ -1819,10 +1808,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s" s="0">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>45</v>
       </c>
       <c r="C2" s="3"/>
@@ -1847,10 +1836,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s" s="0">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>46</v>
       </c>
       <c r="C3" s="3"/>
@@ -1873,10 +1862,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s" s="0">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="3"/>
@@ -1941,10 +1930,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s" s="0">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>48</v>
       </c>
       <c r="C2" s="3"/>
@@ -1978,7 +1967,7 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="42.90625" collapsed="true"/>
+    <col min="11" max="11" width="42.90625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -2017,11 +2006,11 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="231" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>69</v>
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2093,10 +2082,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="362.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s" s="0">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>43</v>
       </c>
       <c r="C2" s="3"/>
@@ -2133,16 +2122,16 @@
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="10" width="8.7265625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="10" width="7.90625" collapsed="true"/>
-    <col min="3" max="9" style="10" width="8.7265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="10" width="10.453125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="10" width="20.7265625" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="10" width="18.0" collapsed="true"/>
-    <col min="13" max="13" style="10" width="8.7265625" collapsed="true"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="10" width="9.36328125" collapsed="true"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="10" width="19.453125" collapsed="true"/>
-    <col min="16" max="16384" style="10" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="8.7265625" style="10" collapsed="1"/>
+    <col min="2" max="2" width="7.90625" style="10" customWidth="1" collapsed="1"/>
+    <col min="3" max="9" width="8.7265625" style="10" collapsed="1"/>
+    <col min="10" max="10" width="10.453125" style="10" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="20.7265625" style="10" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="18" style="10" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="8.7265625" style="10" collapsed="1"/>
+    <col min="14" max="14" width="9.36328125" style="10" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="19.453125" style="10" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="16" max="16384" width="8.7265625" style="10" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
